--- a/Resources/Sheet/Test.xlsx
+++ b/Resources/Sheet/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A0E571-5542-471A-9CE4-9A68AD930701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A832A6-3F85-4859-8692-B3D4F066A883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QSTBKT" sheetId="10" r:id="rId1"/>
@@ -1198,6 +1198,24 @@
     <xf numFmtId="2" fontId="17" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1211,24 +1229,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1581,84 +1581,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32">
-      <c r="A1" s="159"/>
-      <c r="B1" s="159"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="159"/>
-      <c r="G1" s="159"/>
-      <c r="H1" s="159"/>
-      <c r="I1" s="159"/>
-      <c r="J1" s="159"/>
-      <c r="K1" s="159"/>
-      <c r="L1" s="159"/>
-      <c r="M1" s="159"/>
-      <c r="N1" s="159"/>
-      <c r="O1" s="159"/>
+      <c r="A1" s="154"/>
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="154"/>
+      <c r="G1" s="154"/>
+      <c r="H1" s="154"/>
+      <c r="I1" s="154"/>
+      <c r="J1" s="154"/>
+      <c r="K1" s="154"/>
+      <c r="L1" s="154"/>
+      <c r="M1" s="154"/>
+      <c r="N1" s="154"/>
+      <c r="O1" s="154"/>
     </row>
     <row r="2" spans="1:32">
-      <c r="A2" s="159"/>
-      <c r="B2" s="159"/>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="159"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="159"/>
-      <c r="O2" s="159"/>
+      <c r="A2" s="154"/>
+      <c r="B2" s="154"/>
+      <c r="C2" s="154"/>
+      <c r="D2" s="154"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="154"/>
+      <c r="H2" s="154"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="154"/>
+      <c r="K2" s="154"/>
+      <c r="L2" s="154"/>
+      <c r="M2" s="154"/>
+      <c r="N2" s="154"/>
+      <c r="O2" s="154"/>
     </row>
     <row r="3" spans="1:32">
-      <c r="A3" s="160" t="s">
+      <c r="A3" s="155" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="160"/>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160"/>
-      <c r="N3" s="162"/>
-      <c r="O3" s="162"/>
+      <c r="B3" s="155"/>
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="155"/>
+      <c r="K3" s="155"/>
+      <c r="L3" s="155"/>
+      <c r="M3" s="155"/>
+      <c r="N3" s="157"/>
+      <c r="O3" s="157"/>
     </row>
     <row r="4" spans="1:32" ht="33.6" customHeight="1">
-      <c r="A4" s="160"/>
-      <c r="B4" s="160"/>
-      <c r="C4" s="160"/>
-      <c r="D4" s="160"/>
-      <c r="E4" s="160"/>
-      <c r="F4" s="160"/>
-      <c r="G4" s="160"/>
-      <c r="H4" s="160"/>
-      <c r="I4" s="160"/>
-      <c r="J4" s="160"/>
-      <c r="K4" s="160"/>
+      <c r="A4" s="155"/>
+      <c r="B4" s="155"/>
+      <c r="C4" s="155"/>
+      <c r="D4" s="155"/>
+      <c r="E4" s="155"/>
+      <c r="F4" s="155"/>
+      <c r="G4" s="155"/>
+      <c r="H4" s="155"/>
+      <c r="I4" s="155"/>
+      <c r="J4" s="155"/>
+      <c r="K4" s="155"/>
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
       <c r="N4" s="11"/>
       <c r="O4" s="11"/>
     </row>
     <row r="5" spans="1:32">
-      <c r="A5" s="160"/>
-      <c r="B5" s="160"/>
+      <c r="A5" s="155"/>
+      <c r="B5" s="155"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
-      <c r="H5" s="160"/>
+      <c r="H5" s="155"/>
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
@@ -1996,21 +1996,21 @@
       <c r="AF19" s="19"/>
     </row>
     <row r="20" spans="1:32">
-      <c r="A20" s="159"/>
-      <c r="B20" s="159"/>
-      <c r="C20" s="159"/>
-      <c r="D20" s="159"/>
-      <c r="E20" s="159"/>
-      <c r="F20" s="159"/>
-      <c r="G20" s="159"/>
-      <c r="H20" s="159"/>
-      <c r="I20" s="159"/>
-      <c r="J20" s="159"/>
-      <c r="K20" s="159"/>
-      <c r="L20" s="159"/>
-      <c r="M20" s="159"/>
-      <c r="N20" s="159"/>
-      <c r="O20" s="159"/>
+      <c r="A20" s="154"/>
+      <c r="B20" s="154"/>
+      <c r="C20" s="154"/>
+      <c r="D20" s="154"/>
+      <c r="E20" s="154"/>
+      <c r="F20" s="154"/>
+      <c r="G20" s="154"/>
+      <c r="H20" s="154"/>
+      <c r="I20" s="154"/>
+      <c r="J20" s="154"/>
+      <c r="K20" s="154"/>
+      <c r="L20" s="154"/>
+      <c r="M20" s="154"/>
+      <c r="N20" s="154"/>
+      <c r="O20" s="154"/>
       <c r="Q20" s="19"/>
       <c r="R20" s="29"/>
       <c r="S20" s="19"/>
@@ -2029,21 +2029,21 @@
       <c r="AF20" s="19"/>
     </row>
     <row r="21" spans="1:32" ht="18.45" customHeight="1">
-      <c r="A21" s="159"/>
-      <c r="B21" s="159"/>
-      <c r="C21" s="159"/>
-      <c r="D21" s="159"/>
-      <c r="E21" s="159"/>
-      <c r="F21" s="159"/>
-      <c r="G21" s="159"/>
-      <c r="H21" s="159"/>
-      <c r="I21" s="159"/>
-      <c r="J21" s="159"/>
-      <c r="K21" s="159"/>
-      <c r="L21" s="159"/>
-      <c r="M21" s="159"/>
-      <c r="N21" s="159"/>
-      <c r="O21" s="159"/>
+      <c r="A21" s="154"/>
+      <c r="B21" s="154"/>
+      <c r="C21" s="154"/>
+      <c r="D21" s="154"/>
+      <c r="E21" s="154"/>
+      <c r="F21" s="154"/>
+      <c r="G21" s="154"/>
+      <c r="H21" s="154"/>
+      <c r="I21" s="154"/>
+      <c r="J21" s="154"/>
+      <c r="K21" s="154"/>
+      <c r="L21" s="154"/>
+      <c r="M21" s="154"/>
+      <c r="N21" s="154"/>
+      <c r="O21" s="154"/>
       <c r="Q21" s="21"/>
       <c r="R21" s="22"/>
       <c r="S21" s="23"/>
@@ -2062,23 +2062,23 @@
       <c r="AF21" s="23"/>
     </row>
     <row r="22" spans="1:32">
-      <c r="A22" s="160" t="s">
+      <c r="A22" s="155" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="160"/>
-      <c r="C22" s="160"/>
-      <c r="D22" s="160"/>
-      <c r="E22" s="160"/>
-      <c r="F22" s="160"/>
-      <c r="G22" s="160"/>
-      <c r="H22" s="160"/>
-      <c r="I22" s="160"/>
-      <c r="J22" s="160"/>
-      <c r="K22" s="160"/>
-      <c r="L22" s="160"/>
-      <c r="M22" s="160"/>
-      <c r="N22" s="161"/>
-      <c r="O22" s="161"/>
+      <c r="B22" s="155"/>
+      <c r="C22" s="155"/>
+      <c r="D22" s="155"/>
+      <c r="E22" s="155"/>
+      <c r="F22" s="155"/>
+      <c r="G22" s="155"/>
+      <c r="H22" s="155"/>
+      <c r="I22" s="155"/>
+      <c r="J22" s="155"/>
+      <c r="K22" s="155"/>
+      <c r="L22" s="155"/>
+      <c r="M22" s="155"/>
+      <c r="N22" s="156"/>
+      <c r="O22" s="156"/>
       <c r="Q22" s="21"/>
       <c r="R22" s="22"/>
       <c r="S22" s="23"/>
@@ -2097,31 +2097,31 @@
       <c r="AF22" s="23"/>
     </row>
     <row r="23" spans="1:32">
-      <c r="A23" s="160"/>
-      <c r="B23" s="160"/>
-      <c r="C23" s="160"/>
-      <c r="D23" s="160"/>
-      <c r="E23" s="160"/>
-      <c r="F23" s="160"/>
-      <c r="G23" s="160"/>
-      <c r="H23" s="160"/>
-      <c r="I23" s="160"/>
-      <c r="J23" s="160"/>
-      <c r="K23" s="160"/>
+      <c r="A23" s="155"/>
+      <c r="B23" s="155"/>
+      <c r="C23" s="155"/>
+      <c r="D23" s="155"/>
+      <c r="E23" s="155"/>
+      <c r="F23" s="155"/>
+      <c r="G23" s="155"/>
+      <c r="H23" s="155"/>
+      <c r="I23" s="155"/>
+      <c r="J23" s="155"/>
+      <c r="K23" s="155"/>
       <c r="L23" s="10"/>
       <c r="M23" s="10"/>
       <c r="N23" s="11"/>
       <c r="O23" s="11"/>
     </row>
     <row r="24" spans="1:32">
-      <c r="A24" s="160"/>
-      <c r="B24" s="160"/>
+      <c r="A24" s="155"/>
+      <c r="B24" s="155"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
-      <c r="H24" s="160"/>
+      <c r="H24" s="155"/>
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
@@ -2340,84 +2340,84 @@
       <c r="O36" s="28"/>
     </row>
     <row r="37" spans="1:15">
-      <c r="A37" s="159"/>
-      <c r="B37" s="159"/>
-      <c r="C37" s="159"/>
-      <c r="D37" s="159"/>
-      <c r="E37" s="159"/>
-      <c r="F37" s="159"/>
-      <c r="G37" s="159"/>
-      <c r="H37" s="159"/>
-      <c r="I37" s="159"/>
-      <c r="J37" s="159"/>
-      <c r="K37" s="159"/>
-      <c r="L37" s="159"/>
-      <c r="M37" s="159"/>
-      <c r="N37" s="159"/>
-      <c r="O37" s="159"/>
+      <c r="A37" s="154"/>
+      <c r="B37" s="154"/>
+      <c r="C37" s="154"/>
+      <c r="D37" s="154"/>
+      <c r="E37" s="154"/>
+      <c r="F37" s="154"/>
+      <c r="G37" s="154"/>
+      <c r="H37" s="154"/>
+      <c r="I37" s="154"/>
+      <c r="J37" s="154"/>
+      <c r="K37" s="154"/>
+      <c r="L37" s="154"/>
+      <c r="M37" s="154"/>
+      <c r="N37" s="154"/>
+      <c r="O37" s="154"/>
     </row>
     <row r="38" spans="1:15" ht="18.45" customHeight="1">
-      <c r="A38" s="159"/>
-      <c r="B38" s="159"/>
-      <c r="C38" s="159"/>
-      <c r="D38" s="159"/>
-      <c r="E38" s="159"/>
-      <c r="F38" s="159"/>
-      <c r="G38" s="159"/>
-      <c r="H38" s="159"/>
-      <c r="I38" s="159"/>
-      <c r="J38" s="159"/>
-      <c r="K38" s="159"/>
-      <c r="L38" s="159"/>
-      <c r="M38" s="159"/>
-      <c r="N38" s="159"/>
-      <c r="O38" s="159"/>
+      <c r="A38" s="154"/>
+      <c r="B38" s="154"/>
+      <c r="C38" s="154"/>
+      <c r="D38" s="154"/>
+      <c r="E38" s="154"/>
+      <c r="F38" s="154"/>
+      <c r="G38" s="154"/>
+      <c r="H38" s="154"/>
+      <c r="I38" s="154"/>
+      <c r="J38" s="154"/>
+      <c r="K38" s="154"/>
+      <c r="L38" s="154"/>
+      <c r="M38" s="154"/>
+      <c r="N38" s="154"/>
+      <c r="O38" s="154"/>
     </row>
     <row r="39" spans="1:15">
-      <c r="A39" s="160" t="s">
+      <c r="A39" s="155" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="160"/>
-      <c r="C39" s="160"/>
-      <c r="D39" s="160"/>
-      <c r="E39" s="160"/>
-      <c r="F39" s="160"/>
-      <c r="G39" s="160"/>
-      <c r="H39" s="160"/>
-      <c r="I39" s="160"/>
-      <c r="J39" s="160"/>
-      <c r="K39" s="160"/>
-      <c r="L39" s="160"/>
-      <c r="M39" s="160"/>
-      <c r="N39" s="161"/>
-      <c r="O39" s="161"/>
+      <c r="B39" s="155"/>
+      <c r="C39" s="155"/>
+      <c r="D39" s="155"/>
+      <c r="E39" s="155"/>
+      <c r="F39" s="155"/>
+      <c r="G39" s="155"/>
+      <c r="H39" s="155"/>
+      <c r="I39" s="155"/>
+      <c r="J39" s="155"/>
+      <c r="K39" s="155"/>
+      <c r="L39" s="155"/>
+      <c r="M39" s="155"/>
+      <c r="N39" s="156"/>
+      <c r="O39" s="156"/>
     </row>
     <row r="40" spans="1:15">
-      <c r="A40" s="160"/>
-      <c r="B40" s="160"/>
-      <c r="C40" s="160"/>
-      <c r="D40" s="160"/>
-      <c r="E40" s="160"/>
-      <c r="F40" s="160"/>
-      <c r="G40" s="160"/>
-      <c r="H40" s="160"/>
-      <c r="I40" s="160"/>
-      <c r="J40" s="160"/>
-      <c r="K40" s="160"/>
+      <c r="A40" s="155"/>
+      <c r="B40" s="155"/>
+      <c r="C40" s="155"/>
+      <c r="D40" s="155"/>
+      <c r="E40" s="155"/>
+      <c r="F40" s="155"/>
+      <c r="G40" s="155"/>
+      <c r="H40" s="155"/>
+      <c r="I40" s="155"/>
+      <c r="J40" s="155"/>
+      <c r="K40" s="155"/>
       <c r="L40" s="10"/>
       <c r="M40" s="10"/>
       <c r="N40" s="11"/>
       <c r="O40" s="11"/>
     </row>
     <row r="41" spans="1:15">
-      <c r="A41" s="160"/>
-      <c r="B41" s="160"/>
+      <c r="A41" s="155"/>
+      <c r="B41" s="155"/>
       <c r="C41" s="10"/>
       <c r="D41" s="10"/>
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
       <c r="G41" s="10"/>
-      <c r="H41" s="160"/>
+      <c r="H41" s="155"/>
       <c r="I41" s="10"/>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
@@ -2613,84 +2613,84 @@
       <c r="O51" s="28"/>
     </row>
     <row r="52" spans="1:15" ht="18.45" customHeight="1">
-      <c r="A52" s="159"/>
-      <c r="B52" s="159"/>
-      <c r="C52" s="159"/>
-      <c r="D52" s="159"/>
-      <c r="E52" s="159"/>
-      <c r="F52" s="159"/>
-      <c r="G52" s="159"/>
-      <c r="H52" s="159"/>
-      <c r="I52" s="159"/>
-      <c r="J52" s="159"/>
-      <c r="K52" s="159"/>
-      <c r="L52" s="159"/>
-      <c r="M52" s="159"/>
-      <c r="N52" s="159"/>
-      <c r="O52" s="159"/>
+      <c r="A52" s="154"/>
+      <c r="B52" s="154"/>
+      <c r="C52" s="154"/>
+      <c r="D52" s="154"/>
+      <c r="E52" s="154"/>
+      <c r="F52" s="154"/>
+      <c r="G52" s="154"/>
+      <c r="H52" s="154"/>
+      <c r="I52" s="154"/>
+      <c r="J52" s="154"/>
+      <c r="K52" s="154"/>
+      <c r="L52" s="154"/>
+      <c r="M52" s="154"/>
+      <c r="N52" s="154"/>
+      <c r="O52" s="154"/>
     </row>
     <row r="53" spans="1:15">
-      <c r="A53" s="159"/>
-      <c r="B53" s="159"/>
-      <c r="C53" s="159"/>
-      <c r="D53" s="159"/>
-      <c r="E53" s="159"/>
-      <c r="F53" s="159"/>
-      <c r="G53" s="159"/>
-      <c r="H53" s="159"/>
-      <c r="I53" s="159"/>
-      <c r="J53" s="159"/>
-      <c r="K53" s="159"/>
-      <c r="L53" s="159"/>
-      <c r="M53" s="159"/>
-      <c r="N53" s="159"/>
-      <c r="O53" s="159"/>
+      <c r="A53" s="154"/>
+      <c r="B53" s="154"/>
+      <c r="C53" s="154"/>
+      <c r="D53" s="154"/>
+      <c r="E53" s="154"/>
+      <c r="F53" s="154"/>
+      <c r="G53" s="154"/>
+      <c r="H53" s="154"/>
+      <c r="I53" s="154"/>
+      <c r="J53" s="154"/>
+      <c r="K53" s="154"/>
+      <c r="L53" s="154"/>
+      <c r="M53" s="154"/>
+      <c r="N53" s="154"/>
+      <c r="O53" s="154"/>
     </row>
     <row r="54" spans="1:15">
-      <c r="A54" s="160" t="s">
+      <c r="A54" s="155" t="s">
         <v>52</v>
       </c>
-      <c r="B54" s="160"/>
-      <c r="C54" s="160"/>
-      <c r="D54" s="160"/>
-      <c r="E54" s="160"/>
-      <c r="F54" s="160"/>
-      <c r="G54" s="160"/>
-      <c r="H54" s="160"/>
-      <c r="I54" s="160"/>
-      <c r="J54" s="160"/>
-      <c r="K54" s="160"/>
-      <c r="L54" s="160"/>
-      <c r="M54" s="160"/>
-      <c r="N54" s="161"/>
-      <c r="O54" s="161"/>
+      <c r="B54" s="155"/>
+      <c r="C54" s="155"/>
+      <c r="D54" s="155"/>
+      <c r="E54" s="155"/>
+      <c r="F54" s="155"/>
+      <c r="G54" s="155"/>
+      <c r="H54" s="155"/>
+      <c r="I54" s="155"/>
+      <c r="J54" s="155"/>
+      <c r="K54" s="155"/>
+      <c r="L54" s="155"/>
+      <c r="M54" s="155"/>
+      <c r="N54" s="156"/>
+      <c r="O54" s="156"/>
     </row>
     <row r="55" spans="1:15">
-      <c r="A55" s="160"/>
-      <c r="B55" s="160"/>
-      <c r="C55" s="160"/>
-      <c r="D55" s="160"/>
-      <c r="E55" s="160"/>
-      <c r="F55" s="160"/>
-      <c r="G55" s="160"/>
-      <c r="H55" s="160"/>
-      <c r="I55" s="160"/>
-      <c r="J55" s="160"/>
-      <c r="K55" s="160"/>
+      <c r="A55" s="155"/>
+      <c r="B55" s="155"/>
+      <c r="C55" s="155"/>
+      <c r="D55" s="155"/>
+      <c r="E55" s="155"/>
+      <c r="F55" s="155"/>
+      <c r="G55" s="155"/>
+      <c r="H55" s="155"/>
+      <c r="I55" s="155"/>
+      <c r="J55" s="155"/>
+      <c r="K55" s="155"/>
       <c r="L55" s="10"/>
       <c r="M55" s="10"/>
       <c r="N55" s="11"/>
       <c r="O55" s="11"/>
     </row>
     <row r="56" spans="1:15">
-      <c r="A56" s="160"/>
-      <c r="B56" s="160"/>
+      <c r="A56" s="155"/>
+      <c r="B56" s="155"/>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
       <c r="E56" s="10"/>
       <c r="F56" s="10"/>
       <c r="G56" s="10"/>
-      <c r="H56" s="160"/>
+      <c r="H56" s="155"/>
       <c r="I56" s="10"/>
       <c r="J56" s="10"/>
       <c r="K56" s="10"/>
@@ -2812,84 +2812,84 @@
       <c r="O62" s="28"/>
     </row>
     <row r="63" spans="1:15">
-      <c r="A63" s="159"/>
-      <c r="B63" s="159"/>
-      <c r="C63" s="159"/>
-      <c r="D63" s="159"/>
-      <c r="E63" s="159"/>
-      <c r="F63" s="159"/>
-      <c r="G63" s="159"/>
-      <c r="H63" s="159"/>
-      <c r="I63" s="159"/>
-      <c r="J63" s="159"/>
-      <c r="K63" s="159"/>
-      <c r="L63" s="159"/>
-      <c r="M63" s="159"/>
-      <c r="N63" s="159"/>
-      <c r="O63" s="159"/>
+      <c r="A63" s="154"/>
+      <c r="B63" s="154"/>
+      <c r="C63" s="154"/>
+      <c r="D63" s="154"/>
+      <c r="E63" s="154"/>
+      <c r="F63" s="154"/>
+      <c r="G63" s="154"/>
+      <c r="H63" s="154"/>
+      <c r="I63" s="154"/>
+      <c r="J63" s="154"/>
+      <c r="K63" s="154"/>
+      <c r="L63" s="154"/>
+      <c r="M63" s="154"/>
+      <c r="N63" s="154"/>
+      <c r="O63" s="154"/>
     </row>
     <row r="64" spans="1:15">
-      <c r="A64" s="159"/>
-      <c r="B64" s="159"/>
-      <c r="C64" s="159"/>
-      <c r="D64" s="159"/>
-      <c r="E64" s="159"/>
-      <c r="F64" s="159"/>
-      <c r="G64" s="159"/>
-      <c r="H64" s="159"/>
-      <c r="I64" s="159"/>
-      <c r="J64" s="159"/>
-      <c r="K64" s="159"/>
-      <c r="L64" s="159"/>
-      <c r="M64" s="159"/>
-      <c r="N64" s="159"/>
-      <c r="O64" s="159"/>
+      <c r="A64" s="154"/>
+      <c r="B64" s="154"/>
+      <c r="C64" s="154"/>
+      <c r="D64" s="154"/>
+      <c r="E64" s="154"/>
+      <c r="F64" s="154"/>
+      <c r="G64" s="154"/>
+      <c r="H64" s="154"/>
+      <c r="I64" s="154"/>
+      <c r="J64" s="154"/>
+      <c r="K64" s="154"/>
+      <c r="L64" s="154"/>
+      <c r="M64" s="154"/>
+      <c r="N64" s="154"/>
+      <c r="O64" s="154"/>
     </row>
     <row r="65" spans="1:15">
-      <c r="A65" s="160" t="s">
+      <c r="A65" s="155" t="s">
         <v>52</v>
       </c>
-      <c r="B65" s="160"/>
-      <c r="C65" s="160"/>
-      <c r="D65" s="160"/>
-      <c r="E65" s="160"/>
-      <c r="F65" s="160"/>
-      <c r="G65" s="160"/>
-      <c r="H65" s="160"/>
-      <c r="I65" s="160"/>
-      <c r="J65" s="160"/>
-      <c r="K65" s="160"/>
-      <c r="L65" s="160"/>
-      <c r="M65" s="160"/>
-      <c r="N65" s="161"/>
-      <c r="O65" s="161"/>
+      <c r="B65" s="155"/>
+      <c r="C65" s="155"/>
+      <c r="D65" s="155"/>
+      <c r="E65" s="155"/>
+      <c r="F65" s="155"/>
+      <c r="G65" s="155"/>
+      <c r="H65" s="155"/>
+      <c r="I65" s="155"/>
+      <c r="J65" s="155"/>
+      <c r="K65" s="155"/>
+      <c r="L65" s="155"/>
+      <c r="M65" s="155"/>
+      <c r="N65" s="156"/>
+      <c r="O65" s="156"/>
     </row>
     <row r="66" spans="1:15">
-      <c r="A66" s="160"/>
-      <c r="B66" s="160"/>
-      <c r="C66" s="160"/>
-      <c r="D66" s="160"/>
-      <c r="E66" s="160"/>
-      <c r="F66" s="160"/>
-      <c r="G66" s="160"/>
-      <c r="H66" s="160"/>
-      <c r="I66" s="160"/>
-      <c r="J66" s="160"/>
-      <c r="K66" s="160"/>
+      <c r="A66" s="155"/>
+      <c r="B66" s="155"/>
+      <c r="C66" s="155"/>
+      <c r="D66" s="155"/>
+      <c r="E66" s="155"/>
+      <c r="F66" s="155"/>
+      <c r="G66" s="155"/>
+      <c r="H66" s="155"/>
+      <c r="I66" s="155"/>
+      <c r="J66" s="155"/>
+      <c r="K66" s="155"/>
       <c r="L66" s="10"/>
       <c r="M66" s="10"/>
       <c r="N66" s="11"/>
       <c r="O66" s="11"/>
     </row>
     <row r="67" spans="1:15">
-      <c r="A67" s="160"/>
-      <c r="B67" s="160"/>
+      <c r="A67" s="155"/>
+      <c r="B67" s="155"/>
       <c r="C67" s="10"/>
       <c r="D67" s="10"/>
       <c r="E67" s="10"/>
       <c r="F67" s="10"/>
       <c r="G67" s="10"/>
-      <c r="H67" s="160"/>
+      <c r="H67" s="155"/>
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
       <c r="K67" s="10"/>
@@ -3209,32 +3209,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999">
-      <c r="A1" s="163"/>
-      <c r="B1" s="163"/>
-      <c r="C1" s="163"/>
-      <c r="D1" s="163"/>
-      <c r="E1" s="163"/>
-      <c r="F1" s="163"/>
-      <c r="G1" s="163"/>
-      <c r="H1" s="163"/>
+      <c r="A1" s="158"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
     </row>
     <row r="2" spans="1:8" ht="17.399999999999999">
-      <c r="A2" s="164"/>
-      <c r="B2" s="164"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="164"/>
-      <c r="E2" s="164"/>
-      <c r="F2" s="164"/>
-      <c r="G2" s="164"/>
-      <c r="H2" s="164"/>
+      <c r="A2" s="159"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
     </row>
     <row r="3" spans="1:8" ht="17.399999999999999">
-      <c r="A3" s="164"/>
-      <c r="B3" s="164"/>
-      <c r="C3" s="164"/>
-      <c r="D3" s="164"/>
-      <c r="E3" s="164"/>
-      <c r="F3" s="164"/>
+      <c r="A3" s="159"/>
+      <c r="B3" s="159"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="159"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
@@ -3636,20 +3636,20 @@
       <c r="A1" s="34"/>
     </row>
     <row r="2" spans="1:9" ht="18" thickBot="1">
-      <c r="A2" s="154"/>
-      <c r="B2" s="154"/>
-      <c r="C2" s="154"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="158"/>
+      <c r="A2" s="160"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="163"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="162"/>
+      <c r="H2" s="163"/>
+      <c r="I2" s="164"/>
     </row>
     <row r="3" spans="1:9" ht="18" thickBot="1">
-      <c r="A3" s="155"/>
-      <c r="B3" s="155"/>
-      <c r="C3" s="155"/>
+      <c r="A3" s="161"/>
+      <c r="B3" s="161"/>
+      <c r="C3" s="161"/>
       <c r="D3" s="36"/>
       <c r="E3" s="36"/>
       <c r="F3" s="36"/>
